--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_3.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_3.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,7 +362,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Treatment</t>
+          <t>BirthOrder</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.9810697816330481</v>
+        <v>0.3752580933854999</v>
       </c>
       <c r="C2">
-        <v>-1.011445742021168</v>
+        <v>0.8484240030009274</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.5684947617948829</v>
+        <v>0.7545460237392108</v>
       </c>
       <c r="C3">
-        <v>-0.9618119960762025</v>
+        <v>-0.6774698598939108</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.592115466629214</v>
+        <v>-0.5572676748987647</v>
       </c>
       <c r="C4">
-        <v>-0.2759088239239078</v>
+        <v>0.822698409125739</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.7719206973869479</v>
+        <v>-1.295187789762418</v>
       </c>
       <c r="C5">
-        <v>-3.331752699283449</v>
+        <v>-1.385544445829102</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.9088198092121809</v>
+        <v>0.5770789489285082</v>
       </c>
       <c r="C6">
-        <v>0.2262298993166916</v>
+        <v>0.356614398098053</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>1.06348739608985</v>
+        <v>-0.1809307829873942</v>
       </c>
       <c r="C7">
-        <v>0.03159500755769862</v>
+        <v>0.7521982687934123</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.1154662054571691</v>
+        <v>-0.8326477943747556</v>
       </c>
       <c r="C8">
-        <v>0.3958257510892415</v>
+        <v>1.786767553195334</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.6109765180484326</v>
+        <v>1.852468220547357</v>
       </c>
       <c r="C9">
-        <v>0.3742532181769872</v>
+        <v>0.6735203616920475</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.007952175960199762</v>
+        <v>-1.968648098575469</v>
       </c>
       <c r="C10">
-        <v>-0.07352812210104179</v>
+        <v>0.2577529038943117</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.3093370843390823</v>
+        <v>-0.2284428314435442</v>
       </c>
       <c r="C11">
-        <v>0.5636653028719003</v>
+        <v>0.07151484740761205</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.2427559995782418</v>
+        <v>0.5827137591511923</v>
       </c>
       <c r="C12">
-        <v>-0.4486770173647633</v>
+        <v>-0.4164802973741434</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.2842967622272651</v>
+        <v>0.137403352531191</v>
       </c>
       <c r="C13">
-        <v>2.029380713299018</v>
+        <v>-0.4641529628352785</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.7752262645048279</v>
+        <v>-1.471496656440701</v>
       </c>
       <c r="C14">
-        <v>-0.6416200029337119</v>
+        <v>-1.067035371134294</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.7070399195622756</v>
+        <v>1.992924969983397</v>
       </c>
       <c r="C15">
-        <v>0.1077162060851296</v>
+        <v>1.712962943834393</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.7804823398174947</v>
+        <v>-0.7918648531026511</v>
       </c>
       <c r="C16">
-        <v>-0.1103993777574184</v>
+        <v>-0.8305603213106482</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>1.507567403984062</v>
+        <v>1.437630267129506</v>
       </c>
       <c r="C17">
-        <v>1.151760993149333</v>
+        <v>-0.3757611990523256</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.5643050390668899</v>
+        <v>1.648090284340676</v>
       </c>
       <c r="C18">
-        <v>0.8562193714266481</v>
+        <v>-0.2481331638627076</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-0.5838606114120329</v>
+        <v>-2.618550375454762</v>
       </c>
       <c r="C19">
-        <v>0.5142893706460943</v>
+        <v>-0.5601162165209097</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.1587850693174306</v>
+        <v>0.06920118854192465</v>
       </c>
       <c r="C20">
-        <v>0.8513478450493018</v>
+        <v>-0.2705764249627894</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>1.770869505342828</v>
+        <v>0.06466093727474995</v>
       </c>
       <c r="C21">
-        <v>2.581652300026056</v>
+        <v>-0.8504575033774235</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.4412668776407498</v>
+        <v>-0.2545079888521117</v>
       </c>
       <c r="C22">
-        <v>-0.4202733987548668</v>
+        <v>-1.557861776917754</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-1.411843126768232</v>
+        <v>-0.5290829188149869</v>
       </c>
       <c r="C23">
-        <v>-0.3582722394458442</v>
+        <v>-1.060984139879617</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>1.262501331436769</v>
+        <v>0.03002770204264987</v>
       </c>
       <c r="C24">
-        <v>2.351013143644193</v>
+        <v>0.163253576145711</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>-0.2827988512723387</v>
+        <v>1.48525840825279</v>
       </c>
       <c r="C25">
-        <v>-0.5532872009267169</v>
+        <v>-0.578591720779093</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>0.7843162981367414</v>
+        <v>-1.42897838754442</v>
       </c>
       <c r="C26">
-        <v>0.6446563712309206</v>
+        <v>-0.1255607409085289</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>1.01199552812979</v>
+        <v>0.4738605482176956</v>
       </c>
       <c r="C27">
-        <v>0.5615096808921849</v>
+        <v>1.556179918220469</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>-0.7982393908732005</v>
+        <v>-0.2174043115899618</v>
       </c>
       <c r="C28">
-        <v>-1.560935945585365</v>
+        <v>-0.8337654050151376</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-0.8136234876443761</v>
+        <v>-0.07239958369779569</v>
       </c>
       <c r="C29">
-        <v>-0.6414772225362944</v>
+        <v>0.965153582105113</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.1726699405409101</v>
+        <v>0.7529930639848288</v>
       </c>
       <c r="C30">
-        <v>0.07631969668382592</v>
+        <v>1.278491634758206</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.3069692101016294</v>
+        <v>-0.3438473492267223</v>
       </c>
       <c r="C31">
-        <v>1.654336886677885</v>
+        <v>-1.281549284227913</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>-1.204119380002038</v>
+        <v>2.001747230106834</v>
       </c>
       <c r="C32">
-        <v>-1.79164207106451</v>
+        <v>0.09386450237993049</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.5439926673110128</v>
+        <v>-0.8771404554909845</v>
       </c>
       <c r="C33">
-        <v>-1.020492303846271</v>
+        <v>-1.732295246775541</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>-0.5141949640282061</v>
+        <v>0.3226133489051559</v>
       </c>
       <c r="C34">
-        <v>1.159013808602773</v>
+        <v>-0.7653560076638241</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-0.2757434693474368</v>
+        <v>1.640033225714535</v>
       </c>
       <c r="C35">
-        <v>-0.6505190474752967</v>
+        <v>-0.5313280637361677</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>1.377728328989023</v>
+        <v>-0.9548199644220344</v>
       </c>
       <c r="C36">
-        <v>1.659115173975981</v>
+        <v>-0.2629229642528441</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-0.7668391230439606</v>
+        <v>0.1770666839926108</v>
       </c>
       <c r="C37">
-        <v>-0.1692962512399248</v>
+        <v>0.7479401294655641</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>0.8357085634496416</v>
+        <v>-1.906999765151595</v>
       </c>
       <c r="C38">
-        <v>1.011941499407242</v>
+        <v>0.7189287951182143</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>-0.1404648680289611</v>
+        <v>0.8224828657868334</v>
       </c>
       <c r="C39">
-        <v>-1.009246680961481</v>
+        <v>0.344073615960435</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.7988433639130034</v>
+        <v>0.08467619166851426</v>
       </c>
       <c r="C40">
-        <v>-0.05138043263007153</v>
+        <v>-1.012299862088836</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.2339319716566019</v>
+        <v>0.792771302671502</v>
       </c>
       <c r="C41">
-        <v>-1.012716097374459</v>
+        <v>2.413977455312083</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.6450236788585454</v>
+        <v>-0.7260043024220684</v>
       </c>
       <c r="C42">
-        <v>-1.010255671398642</v>
+        <v>-0.8823848279183621</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>-0.9993024078546393</v>
+        <v>-0.03587809026498407</v>
       </c>
       <c r="C43">
-        <v>-0.2621205713328212</v>
+        <v>-0.5046097552734019</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>1.699266953574721</v>
+        <v>0.1803661475844701</v>
       </c>
       <c r="C44">
-        <v>1.319404729578192</v>
+        <v>0.4961681651255613</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.1475030389915161</v>
+        <v>-2.302978179593435</v>
       </c>
       <c r="C45">
-        <v>1.054076878844178</v>
+        <v>-1.647625919739334</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>1.287186695330809</v>
+        <v>0.5183317455191701</v>
       </c>
       <c r="C46">
-        <v>0.4091417128691711</v>
+        <v>-0.9753913706669346</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.3271519004989704</v>
+        <v>0.4578951441355987</v>
       </c>
       <c r="C47">
-        <v>0.06260188659254448</v>
+        <v>-0.414531232365188</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>0.4260860577394294</v>
+        <v>0.7265133441137257</v>
       </c>
       <c r="C48">
-        <v>-0.4121622130577534</v>
+        <v>0.4586795621691938</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-0.3505783684210156</v>
+        <v>-0.3885241406593024</v>
       </c>
       <c r="C49">
-        <v>-0.2721540715840326</v>
+        <v>0.01808264969601853</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>-1.840083515773731</v>
+        <v>-0.522424154142326</v>
       </c>
       <c r="C50">
-        <v>0.2159214035008077</v>
+        <v>-1.150019430628928</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,1960 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.9366158472467301</v>
+        <v>-0.2809725994894245</v>
       </c>
       <c r="C51">
-        <v>1.016918475667375</v>
+        <v>-0.1873126929555705</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>0.135188462968318</v>
+      </c>
+      <c r="C52">
+        <v>-1.161315398600466</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>1.229626901125245</v>
+      </c>
+      <c r="C53">
+        <v>0.4294140171088625</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>1.601463252853785</v>
+      </c>
+      <c r="C54">
+        <v>0.144938912422474</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>0.34277920030908</v>
+      </c>
+      <c r="C55">
+        <v>-1.60285403411076</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>-0.274977766014857</v>
+      </c>
+      <c r="C56">
+        <v>0.008886425470838191</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>-0.8759209906232813</v>
+      </c>
+      <c r="C57">
+        <v>-0.8731403818967043</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>-1.055814242950833</v>
+      </c>
+      <c r="C58">
+        <v>-0.802474517549145</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>-2.332901021618428</v>
+      </c>
+      <c r="C59">
+        <v>-1.438921100243709</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>-0.6213619375801347</v>
+      </c>
+      <c r="C60">
+        <v>-0.8393106245960184</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>-0.01495601779429323</v>
+      </c>
+      <c r="C61">
+        <v>-0.3006726068131751</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>-1.325282372706114</v>
+      </c>
+      <c r="C62">
+        <v>-1.437002846790532</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>-0.4558195189800779</v>
+      </c>
+      <c r="C63">
+        <v>0.1893052427270229</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>-0.6527311413299087</v>
+      </c>
+      <c r="C64">
+        <v>0.7094281860531406</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>-0.01261268203233488</v>
+      </c>
+      <c r="C65">
+        <v>-0.06413518524296613</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B66">
+        <v>1.197299504198468</v>
+      </c>
+      <c r="C66">
+        <v>0.01877419537756658</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B67">
+        <v>-0.2650674919686386</v>
+      </c>
+      <c r="C67">
+        <v>-0.396770690637836</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B68">
+        <v>-1.051480146337066</v>
+      </c>
+      <c r="C68">
+        <v>0.7493732608417041</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B69">
+        <v>0.9369073291119037</v>
+      </c>
+      <c r="C69">
+        <v>0.03300935489488799</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B70">
+        <v>0.01732050244597009</v>
+      </c>
+      <c r="C70">
+        <v>-1.817887507489598</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B71">
+        <v>0.2727115699467746</v>
+      </c>
+      <c r="C71">
+        <v>1.979516356732197</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B72">
+        <v>0.04920139907280425</v>
+      </c>
+      <c r="C72">
+        <v>-0.5996957658584943</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B73">
+        <v>0.9420079143955666</v>
+      </c>
+      <c r="C73">
+        <v>0.573204898772345</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B74">
+        <v>0.2210943080185785</v>
+      </c>
+      <c r="C74">
+        <v>-0.8590814946124582</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B75">
+        <v>1.277107251162114</v>
+      </c>
+      <c r="C75">
+        <v>1.828214302865725</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B76">
+        <v>-1.551790903479547</v>
+      </c>
+      <c r="C76">
+        <v>-1.155231960761017</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B77">
+        <v>-0.4203391665949638</v>
+      </c>
+      <c r="C77">
+        <v>-0.2173542390622567</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B78">
+        <v>0.7737731191607385</v>
+      </c>
+      <c r="C78">
+        <v>0.5215359680464797</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B79">
+        <v>0.4948147775453671</v>
+      </c>
+      <c r="C79">
+        <v>0.7459617148718672</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B80">
+        <v>1.079364690220114</v>
+      </c>
+      <c r="C80">
+        <v>0.05958811935728264</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B81">
+        <v>-1.319597604499073</v>
+      </c>
+      <c r="C81">
+        <v>-1.387738918174707</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B82">
+        <v>0.3591789656198278</v>
+      </c>
+      <c r="C82">
+        <v>0.335967763032695</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B83">
+        <v>2.227763978642911</v>
+      </c>
+      <c r="C83">
+        <v>0.784185025092185</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B84">
+        <v>0.2781743593588411</v>
+      </c>
+      <c r="C84">
+        <v>0.1381792202853691</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B85">
+        <v>-1.026836506870724</v>
+      </c>
+      <c r="C85">
+        <v>-0.7170566440740416</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B86">
+        <v>-1.050446936134237</v>
+      </c>
+      <c r="C86">
+        <v>0.6004311802861929</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B87">
+        <v>-1.569320307651747</v>
+      </c>
+      <c r="C87">
+        <v>-0.7808266064736887</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>-0.1701993569288799</v>
+      </c>
+      <c r="C88">
+        <v>-0.8467395018548365</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>-1.160415868658254</v>
+      </c>
+      <c r="C89">
+        <v>-0.3010881138214684</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B90">
+        <v>0.3714145703499916</v>
+      </c>
+      <c r="C90">
+        <v>-0.4352018722106896</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B91">
+        <v>0.0809065946399718</v>
+      </c>
+      <c r="C91">
+        <v>0.8477784767544446</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B92">
+        <v>-0.6372887029913543</v>
+      </c>
+      <c r="C92">
+        <v>-1.499100034707522</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="B93">
+        <v>0.7302708449508772</v>
+      </c>
+      <c r="C93">
+        <v>2.435091086565955</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="B94">
+        <v>-0.9513982726058542</v>
+      </c>
+      <c r="C94">
+        <v>-1.820396959378466</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="B95">
+        <v>-0.1528033219745365</v>
+      </c>
+      <c r="C95">
+        <v>-0.7896685489494499</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="B96">
+        <v>-1.018214007277784</v>
+      </c>
+      <c r="C96">
+        <v>-0.3309991732277757</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="B97">
+        <v>0.5590926715948883</v>
+      </c>
+      <c r="C97">
+        <v>1.884403513504317</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="B98">
+        <v>-0.5118643776280458</v>
+      </c>
+      <c r="C98">
+        <v>-1.759684753667676</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B99">
+        <v>-0.9094702948134172</v>
+      </c>
+      <c r="C99">
+        <v>0.08028134786049579</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B100">
+        <v>-0.3755475125559738</v>
+      </c>
+      <c r="C100">
+        <v>-0.962453000053579</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B101">
+        <v>-1.092856843051097</v>
+      </c>
+      <c r="C101">
+        <v>2.158405208556642</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>-0.1760383978366127</v>
+      </c>
+      <c r="C102">
+        <v>0.2213652139813408</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>-1.868897179343206</v>
+      </c>
+      <c r="C103">
+        <v>-0.361728404655702</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>0.3451343985633753</v>
+      </c>
+      <c r="C104">
+        <v>-1.565532443756931</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B105">
+        <v>0.01557830155019569</v>
+      </c>
+      <c r="C105">
+        <v>0.8944361493108332</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>0.1321335272951495</v>
+      </c>
+      <c r="C106">
+        <v>0.8130976130006891</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>-0.7487421993802861</v>
+      </c>
+      <c r="C107">
+        <v>-0.747478356099782</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>-0.9905142114420004</v>
+      </c>
+      <c r="C108">
+        <v>-0.4471257525666299</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B109">
+        <v>-1.199052424945358</v>
+      </c>
+      <c r="C109">
+        <v>-0.6504250415731299</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>-0.839416443327528</v>
+      </c>
+      <c r="C110">
+        <v>0.2606139754965315</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>0.3298625565437154</v>
+      </c>
+      <c r="C111">
+        <v>-1.058085884798944</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>-1.533424769310529</v>
+      </c>
+      <c r="C112">
+        <v>0.02612013290355297</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>-0.5503668627703224</v>
+      </c>
+      <c r="C113">
+        <v>-0.2237506240890644</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>-1.42414724398722</v>
+      </c>
+      <c r="C114">
+        <v>-0.4282839633476629</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>-0.3653330085587847</v>
+      </c>
+      <c r="C115">
+        <v>1.244479115919743</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>1.409291432726206</v>
+      </c>
+      <c r="C116">
+        <v>-1.284266544057753</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>-0.4643608730396582</v>
+      </c>
+      <c r="C117">
+        <v>0.1460868790341398</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>0.5554799287261397</v>
+      </c>
+      <c r="C118">
+        <v>-0.7283215789073886</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>1.398747498442922</v>
+      </c>
+      <c r="C119">
+        <v>-0.2894063249241375</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>1.774843630627475</v>
+      </c>
+      <c r="C120">
+        <v>1.502223510326198</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B121">
+        <v>0.7493322806047401</v>
+      </c>
+      <c r="C121">
+        <v>1.746159258535349</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>0.7822840062266694</v>
+      </c>
+      <c r="C122">
+        <v>-0.6569758875003515</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>0.5815436063175413</v>
+      </c>
+      <c r="C123">
+        <v>0.9164650317033592</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>0.8278360940995046</v>
+      </c>
+      <c r="C124">
+        <v>1.110611150171776</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>0.2052875594983168</v>
+      </c>
+      <c r="C125">
+        <v>-0.04913402287306463</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B126">
+        <v>-1.054544710281502</v>
+      </c>
+      <c r="C126">
+        <v>-0.8860508906582463</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>0.6291782237984966</v>
+      </c>
+      <c r="C127">
+        <v>0.2746674171958186</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="B128">
+        <v>-0.563933618563595</v>
+      </c>
+      <c r="C128">
+        <v>0.291469346985705</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B129">
+        <v>1.81787483839646</v>
+      </c>
+      <c r="C129">
+        <v>0.461373374300707</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="B130">
+        <v>-0.7224800495101226</v>
+      </c>
+      <c r="C130">
+        <v>-0.4083121753483422</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B131">
+        <v>0.5885047321208787</v>
+      </c>
+      <c r="C131">
+        <v>0.5344566761644416</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>-1.041002576060004</v>
+      </c>
+      <c r="C132">
+        <v>0.664782025829288</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B133">
+        <v>1.460944080908409</v>
+      </c>
+      <c r="C133">
+        <v>0.7566863773469018</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B134">
+        <v>-1.012078578574906</v>
+      </c>
+      <c r="C134">
+        <v>0.2644967764002809</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B135">
+        <v>-0.01030508715668251</v>
+      </c>
+      <c r="C135">
+        <v>-1.789005406319137</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>-0.6011590578330892</v>
+      </c>
+      <c r="C136">
+        <v>1.07923133215934</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B137">
+        <v>0.02794733620701164</v>
+      </c>
+      <c r="C137">
+        <v>-0.04983065077414664</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B138">
+        <v>1.880522267251699</v>
+      </c>
+      <c r="C138">
+        <v>-0.2560130935076171</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B139">
+        <v>0.7555849514368018</v>
+      </c>
+      <c r="C139">
+        <v>-1.929518611790477</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>-0.309803542168104</v>
+      </c>
+      <c r="C140">
+        <v>0.3251623060900025</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>0.2048449688413734</v>
+      </c>
+      <c r="C141">
+        <v>-0.636020293813784</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="B142">
+        <v>-0.4444236194464139</v>
+      </c>
+      <c r="C142">
+        <v>-0.2444123509985014</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B143">
+        <v>-1.796714771139145</v>
+      </c>
+      <c r="C143">
+        <v>-0.847749761829237</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B144">
+        <v>-0.89530772993039</v>
+      </c>
+      <c r="C144">
+        <v>0.7734555982323219</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B145">
+        <v>0.5277022007363289</v>
+      </c>
+      <c r="C145">
+        <v>-0.5750634495194048</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>0.7433155921360873</v>
+      </c>
+      <c r="C146">
+        <v>-0.1549739380381188</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>-0.4145981473841575</v>
+      </c>
+      <c r="C147">
+        <v>-0.2807350771460124</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>-0.4530672587202821</v>
+      </c>
+      <c r="C148">
+        <v>-0.6708830472336972</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B149">
+        <v>-0.2096410856437368</v>
+      </c>
+      <c r="C149">
+        <v>-1.038592031334961</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B150">
+        <v>0.3109364257605252</v>
+      </c>
+      <c r="C150">
+        <v>-0.1268027809289166</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B151">
+        <v>1.562530423778977</v>
+      </c>
+      <c r="C151">
+        <v>0.2483537672237605</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="B152">
+        <v>-0.4894065795199396</v>
+      </c>
+      <c r="C152">
+        <v>-0.7788768760325004</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B153">
+        <v>0.3735520717808369</v>
+      </c>
+      <c r="C153">
+        <v>0.08906052883753646</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="B154">
+        <v>0.8905278860409083</v>
+      </c>
+      <c r="C154">
+        <v>1.045677167950264</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B155">
+        <v>-0.5310105052794041</v>
+      </c>
+      <c r="C155">
+        <v>0.3478637912901553</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B156">
+        <v>-0.8403295963000913</v>
+      </c>
+      <c r="C156">
+        <v>-0.3382153653481074</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B157">
+        <v>-0.4807703650911681</v>
+      </c>
+      <c r="C157">
+        <v>1.519008835507378</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B158">
+        <v>0.8075533177795973</v>
+      </c>
+      <c r="C158">
+        <v>0.1057440567034464</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B159">
+        <v>0.04813045201179165</v>
+      </c>
+      <c r="C159">
+        <v>0.007345103154659716</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="B160">
+        <v>0.1687599786027468</v>
+      </c>
+      <c r="C160">
+        <v>0.3274450233214439</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="B161">
+        <v>1.304201422627669</v>
+      </c>
+      <c r="C161">
+        <v>0.5332951683411215</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B162">
+        <v>0.07001876740181556</v>
+      </c>
+      <c r="C162">
+        <v>0.1062792781709363</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B163">
+        <v>-0.9462228005465616</v>
+      </c>
+      <c r="C163">
+        <v>-1.853785624485943</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="B164">
+        <v>0.9660929514685535</v>
+      </c>
+      <c r="C164">
+        <v>0.8954112964054305</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="B165">
+        <v>0.1896755214732979</v>
+      </c>
+      <c r="C165">
+        <v>1.311258678926111</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="B166">
+        <v>0.9446155268343995</v>
+      </c>
+      <c r="C166">
+        <v>0.7265605253034251</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B167">
+        <v>-2.111429499743263</v>
+      </c>
+      <c r="C167">
+        <v>-1.221960763022259</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B168">
+        <v>1.193192046937792</v>
+      </c>
+      <c r="C168">
+        <v>0.9957642690228743</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="B169">
+        <v>-0.3811876224272004</v>
+      </c>
+      <c r="C169">
+        <v>0.4410575597393961</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="B170">
+        <v>0.2377407026503432</v>
+      </c>
+      <c r="C170">
+        <v>0.6218894706274749</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B171">
+        <v>0.3518596646065044</v>
+      </c>
+      <c r="C171">
+        <v>1.54534981391323</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="B172">
+        <v>0.8988121715969297</v>
+      </c>
+      <c r="C172">
+        <v>0.3648374654760553</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B173">
+        <v>0.1165155751452442</v>
+      </c>
+      <c r="C173">
+        <v>-0.3547543790059483</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="B174">
+        <v>0.03031626237584386</v>
+      </c>
+      <c r="C174">
+        <v>-1.367132857277771</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B175">
+        <v>-1.343442123791535</v>
+      </c>
+      <c r="C175">
+        <v>-0.5635476674567242</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B176">
+        <v>-0.541827182899946</v>
+      </c>
+      <c r="C176">
+        <v>-0.3421956201262871</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="B177">
+        <v>0.5128914549171698</v>
+      </c>
+      <c r="C177">
+        <v>-0.5669255533474515</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B178">
+        <v>0.9651704787246426</v>
+      </c>
+      <c r="C178">
+        <v>0.3539210193718006</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="B179">
+        <v>0.8215266739668996</v>
+      </c>
+      <c r="C179">
+        <v>0.05305566366339826</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="B180">
+        <v>-0.1853269990610641</v>
+      </c>
+      <c r="C180">
+        <v>0.7667952077752884</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B181">
+        <v>-1.289551850628908</v>
+      </c>
+      <c r="C181">
+        <v>-0.1211869980163051</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="B182">
+        <v>0.6480871362350118</v>
+      </c>
+      <c r="C182">
+        <v>1.087478965324893</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="B183">
+        <v>0.2119609928348117</v>
+      </c>
+      <c r="C183">
+        <v>0.5590003432620453</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="B184">
+        <v>-0.9366065069846385</v>
+      </c>
+      <c r="C184">
+        <v>-0.1327847515480566</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B185">
+        <v>-1.415045976177973</v>
+      </c>
+      <c r="C185">
+        <v>0.4599330565948813</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B186">
+        <v>-0.9845346737090979</v>
+      </c>
+      <c r="C186">
+        <v>-0.6318756529809043</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="B187">
+        <v>-0.4066814956645793</v>
+      </c>
+      <c r="C187">
+        <v>0.1955243897040278</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B188">
+        <v>0.1987060829554331</v>
+      </c>
+      <c r="C188">
+        <v>0.6782706921651962</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B189">
+        <v>-0.04795754714034168</v>
+      </c>
+      <c r="C189">
+        <v>0.7094104479244999</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B190">
+        <v>0.5385094247827255</v>
+      </c>
+      <c r="C190">
+        <v>-0.1229556909515507</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B191">
+        <v>1.304604864605342</v>
+      </c>
+      <c r="C191">
+        <v>-1.799674175111657</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B192">
+        <v>-0.2902823924439785</v>
+      </c>
+      <c r="C192">
+        <v>1.413654830728373</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B193">
+        <v>0.7316266211929476</v>
+      </c>
+      <c r="C193">
+        <v>-0.6206937327091941</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B194">
+        <v>0.4509661639543235</v>
+      </c>
+      <c r="C194">
+        <v>0.1910514217812689</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B195">
+        <v>-0.5668033736847264</v>
+      </c>
+      <c r="C195">
+        <v>0.274728291365484</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B196">
+        <v>1.552116858690517</v>
+      </c>
+      <c r="C196">
+        <v>1.554750442641056</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B197">
+        <v>-0.08417767785316832</v>
+      </c>
+      <c r="C197">
+        <v>-0.09261943762658208</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B198">
+        <v>-0.2981120400039585</v>
+      </c>
+      <c r="C198">
+        <v>-1.601321108675394</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B199">
+        <v>0.3468209357212526</v>
+      </c>
+      <c r="C199">
+        <v>-0.4858167563407327</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B200">
+        <v>0.6199094621106545</v>
+      </c>
+      <c r="C200">
+        <v>1.377560535440984</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B201">
+        <v>-2.033325394182579</v>
+      </c>
+      <c r="C201">
+        <v>-0.7888178749495965</v>
       </c>
     </row>
   </sheetData>
